--- a/08_tables/q8_autocorrelation_and_trend_correlation.xlsx
+++ b/08_tables/q8_autocorrelation_and_trend_correlation.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q8_autocorrelation_and_trend_correlation.xlsx
+++ b/08_tables/q8_autocorrelation_and_trend_correlation.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Autocorrelation with lag 1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>N autocorrelation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Trend correlation</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N trend correlation</t>
         </is>
@@ -462,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9258904252888899</v>
+        <v>0.9258904252888895</v>
       </c>
       <c r="C2" t="n">
         <v>735</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7124345143856256</v>
+        <v>-0.7124345143856258</v>
       </c>
       <c r="E2" t="n">
         <v>750</v>
@@ -481,7 +469,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9992769025502811</v>
+        <v>0.9992769025502813</v>
       </c>
       <c r="C3" t="n">
         <v>735</v>
@@ -500,7 +488,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9991053691484881</v>
+        <v>0.9991053691484878</v>
       </c>
       <c r="C4" t="n">
         <v>725</v>
@@ -519,13 +507,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9862451046703793</v>
+        <v>0.9862451046703795</v>
       </c>
       <c r="C5" t="n">
         <v>725</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05694971579071797</v>
+        <v>-0.05694971579071802</v>
       </c>
       <c r="E5" t="n">
         <v>740</v>
@@ -544,7 +532,7 @@
         <v>735</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2056386165546836</v>
+        <v>0.2056386165546837</v>
       </c>
       <c r="E6" t="n">
         <v>750</v>
@@ -557,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9706940914163369</v>
+        <v>0.9706940914163366</v>
       </c>
       <c r="C7" t="n">
         <v>725</v>
@@ -576,13 +564,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9666202364499854</v>
+        <v>0.9666202364499856</v>
       </c>
       <c r="C8" t="n">
         <v>726</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2228973982928158</v>
+        <v>0.2228973982928157</v>
       </c>
       <c r="E8" t="n">
         <v>741</v>
@@ -595,13 +583,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9895332697129974</v>
+        <v>0.9895332697129976</v>
       </c>
       <c r="C9" t="n">
         <v>573</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06923761460257809</v>
+        <v>-0.06923761460257803</v>
       </c>
       <c r="E9" t="n">
         <v>588</v>
@@ -614,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9641510084248979</v>
+        <v>0.9641510084248976</v>
       </c>
       <c r="C10" t="n">
         <v>573</v>
@@ -633,13 +621,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9998998362708847</v>
+        <v>0.9998998362708842</v>
       </c>
       <c r="C11" t="n">
         <v>726</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09986487739300696</v>
+        <v>0.09986487739300692</v>
       </c>
       <c r="E11" t="n">
         <v>741</v>
@@ -658,7 +646,7 @@
         <v>735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05428036460153166</v>
+        <v>0.05428036460153164</v>
       </c>
       <c r="E12" t="n">
         <v>750</v>
